--- a/docs/downloads/10/tbl_feux_marovoay_tous.xlsx
+++ b/docs/downloads/10/tbl_feux_marovoay_tous.xlsx
@@ -374,7 +374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -389,7 +389,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -404,7 +404,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -419,7 +419,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -434,7 +434,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -449,7 +449,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -569,7 +569,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
